--- a/ConfigWorkspace/Data/tile_effect.xlsx
+++ b/ConfigWorkspace/Data/tile_effect.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -35,9 +35,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
     <t>##type</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>TileEffectType</t>
   </si>
   <si>
@@ -71,10 +65,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>bool</t>
+    <t>(list#sep=;),float</t>
+  </si>
+  <si>
+    <t>(list#sep=;),bool</t>
   </si>
   <si>
     <t>##group</t>
@@ -86,9 +80,6 @@
     <t>##comment</t>
   </si>
   <si>
-    <t>效果id</t>
-  </si>
-  <si>
     <t>效果类型</t>
   </si>
   <si>
@@ -119,36 +110,36 @@
     <t>减速</t>
   </si>
   <si>
-    <t>减速50%</t>
-  </si>
-  <si>
     <t>value1=速度倍率</t>
   </si>
   <si>
+    <t>打滑</t>
+  </si>
+  <si>
+    <t>冰面打滑</t>
+  </si>
+  <si>
     <t>滑行</t>
   </si>
   <si>
-    <t>打滑1格</t>
+    <t>打滑value1格</t>
   </si>
   <si>
     <t>value1=滑行距离(格)</t>
   </si>
   <si>
-    <t>打滑2格</t>
+    <t>1;2</t>
   </si>
   <si>
     <t>击退</t>
   </si>
   <si>
-    <t>击退1格</t>
+    <t>击退value1格</t>
   </si>
   <si>
     <t>value1=击退距离(格)</t>
   </si>
   <si>
-    <t>击退2格</t>
-  </si>
-  <si>
     <t>阻挡</t>
   </si>
   <si>
@@ -173,7 +164,7 @@
     <t>藤蔓缠绕定身</t>
   </si>
   <si>
-    <t>value1=可定身敌人数量？</t>
+    <t>value1=最多可定身敌人数量</t>
   </si>
   <si>
     <t>瞬时伤害</t>
@@ -185,7 +176,7 @@
     <t>value1=伤害值，flag=一次性效果</t>
   </si>
   <si>
-    <t>地块伤害1（一次性）</t>
+    <t>FALSE;TRUE</t>
   </si>
   <si>
     <t>持续伤害</t>
@@ -197,7 +188,13 @@
     <t>value1=每次伤害值，interval=伤害间隔</t>
   </si>
   <si>
-    <t>0.5持续伤害3s</t>
+    <t>0.5;1</t>
+  </si>
+  <si>
+    <t>1;1</t>
+  </si>
+  <si>
+    <t>FALSE;FALSE</t>
   </si>
   <si>
     <t>温湿度继承</t>
@@ -212,7 +209,7 @@
     <t>清除植物</t>
   </si>
   <si>
-    <t>value1=清除范围（格）？</t>
+    <t>value1=清除范围（十字）</t>
   </si>
 </sst>
 </file>
@@ -225,7 +222,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,15 +232,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -711,133 +699,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -846,10 +834,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1204,19 +1192,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="13.1" customWidth="1"/>
-    <col min="3" max="3" width="16.0636363636364" customWidth="1"/>
-    <col min="4" max="4" width="23.3272727272727" customWidth="1"/>
-    <col min="5" max="5" width="42.3454545454545" customWidth="1"/>
-    <col min="6" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16.0636363636364" customWidth="1"/>
+    <col min="3" max="3" width="25.6818181818182" customWidth="1"/>
+    <col min="4" max="4" width="42.3454545454545" customWidth="1"/>
+    <col min="5" max="5" width="20.2181818181818" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="13.6363636363636" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1241,532 +1230,397 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" ht="17" customHeight="1" spans="1:9">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5"/>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5"/>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="5"/>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="5"/>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5"/>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4"/>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
+    <row r="7" spans="1:9">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5"/>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
-        <v>2001</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="2" t="s">
+    <row r="8" spans="1:9">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4"/>
+      <c r="D8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <v>3001</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="2" t="s">
+    <row r="9" spans="1:9">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:9">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4"/>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4"/>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>3002</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2">
+    <row r="11" spans="1:9">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" ht="28" spans="1:9">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4"/>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4"/>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>4001</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2">
-        <v>4002</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" customFormat="1" spans="1:10">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
-        <v>5001</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2">
-        <v>6001</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2">
-        <v>7001</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2">
-        <v>8001</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2">
-        <v>8002</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2">
-        <v>9001</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2">
-        <v>9002</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" ht="28" spans="1:10">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2">
-        <v>10001</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2">
-        <v>11001</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:10">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+    <row r="17" customFormat="1" spans="1:9">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
